--- a/www/download/COUNTRY.BEL.WIOD13.xlsx
+++ b/www/download/COUNTRY.BEL.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Bélgica</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.7299483476926</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.767200650712243</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.885559181066731</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.89852905874464</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.938262384526172</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>1.08271977599631</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1.1165698681726</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.05752964628676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>0.884017016719317</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.803923186934283</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.803793926163139</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.796431999331189</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.729660720440948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.679902075880751</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.71694868628827</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>-0.473267816049411</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.878</t>
+          <t>-0.479802493529803</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.904</t>
+          <t>-0.450956739306515</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>-0.444298422443381</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.028</t>
+          <t>-0.499614150338939</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>-0.497413172267108</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.165</t>
+          <t>-0.52320178911202</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>-0.555105132917792</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>-0.609739203476388</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.199</t>
+          <t>-0.652652136267561</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.258</t>
+          <t>-0.647455497569256</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.308</t>
+          <t>-0.642656028864535</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.378</t>
+          <t>-0.620966450748709</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>-0.565228865227056</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.438</t>
+          <t>-0.585232980862737</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>-0.165896409948928</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>-0.182127230793031</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.198</t>
+          <t>-0.14166432327897</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.268</t>
+          <t>-0.135540093135258</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.323</t>
+          <t>-0.216755039543478</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>-0.224588257257891</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.266524360186788</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>-0.322453427467491</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.472</t>
+          <t>-0.42591877027464</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.507</t>
+          <t>-0.466818026877302</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.563</t>
+          <t>-0.454815796092454</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>-0.443482975419388</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.672</t>
+          <t>-0.41903588271488</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>-0.34631538097527</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>-0.378796539020013</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>-0.0938474873793222</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>-0.108960960536042</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>-0.063536502922251</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>-0.0548668784583264</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>-0.155528103544503</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>-0.144824082401787</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>-0.190060345599167</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>-0.256729731016777</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>-0.463480532927886</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>-0.410863865777853</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>-0.395893770555358</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>-0.383341072102482</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>-0.323560775473188</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>-0.247877674805566</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>-0.286884772952006</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>11795699207.542</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>11136798877.6232</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>10598389539.6188</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>10777325995.7022</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>11121922224.4909</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>11897304974.5574</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>11867285299.632</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>11493336647.5636</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>12395151016.6241</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>13183274136.5104</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>12692033190.9768</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>13676094132.3255</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>14221384783.5633</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>16584705298.3802</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>12440435615.406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.58</t>
+          <t>5789924273.96474</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>5901733982.96789</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>5705353345.29825</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>5775247085.73027</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>6542399481.87736</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>6790449694.63374</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7301252824.01896</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18.01</t>
+          <t>7875261420.37654</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.66</t>
+          <t>9602628260.51864</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>10185704076.5201</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19.54</t>
+          <t>10107711126.3251</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>10087817940.911</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>20.37</t>
+          <t>9731546054.23637</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>8880990299.43425</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>9183682932.88638</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>857413.069534259</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.79</t>
+          <t>850907.426207846</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>897014.076328498</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>897558.806632495</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>960709.209402664</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>49.98</t>
+          <t>1038282.02387961</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>1026296.90289345</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>968692.287226128</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>50.25</t>
+          <t>872418.557470349</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>805883.96767791</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.45</t>
+          <t>771508.442178694</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.16</t>
+          <t>739599.393276983</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>659558.711576959</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>678557.13892158</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>56.94</t>
+          <t>617645.82888524</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.86</t>
+          <t>20591.1517595347</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>20482.0580133694</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>20435.6736495073</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>20460.5499682048</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>21105.5945557966</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>22437.6433531567</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>21937.7798269552</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>21999.3494574964</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>23535.961312143</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>25936.9955531466</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>27510.8294565259</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>29130.3741109324</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>33330.3243267202</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>37114.1822426283</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>33884.7816910526</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>91832.7392740208</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>87347.6381131839</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12.22</t>
+          <t>82590.9818304017</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>83524.6889415128</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>88066.990650333</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.73</t>
+          <t>98019.1394396157</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12.97</t>
+          <t>95209.8107929586</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>94266.9135776621</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>109507.383792793</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>128356.182581801</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>132346.564258839</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>149461.839488098</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>14.86</t>
+          <t>175827.846172081</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>227010.119117819</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>158838.235159117</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>-0.20636267720071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>-0.223008015401268</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>-0.185922462834386</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>-0.181125944951323</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>-0.263511802764856</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>-0.266307796383915</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>-0.307269571139718</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>-0.360897406278184</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>-0.476351696266912</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>-0.501045783205563</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>-0.491081617221662</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>-0.482722623409206</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>-0.453057102095001</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>-0.391948440666127</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>-0.42458814850012</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>62222.717238969</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>61422.0419641718</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>54932.4553463548</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>58035.8306529816</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>57184.7261518678</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>54091.3048433165</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>34.07</t>
+          <t>56030.3001531262</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>58895.1190253721</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>72794.3248327627</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>85557.9359023419</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>90834.3468905472</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>96526.9172804707</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>109574.060944313</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>124123.390379445</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>119239.864519896</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7299483476926</t>
+          <t>1827.09586224109</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.767200650712243</t>
+          <t>1859.88057495902</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885559181066731</t>
+          <t>1783.77467281197</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89852905874464</t>
+          <t>1767.32125212499</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262384526172</t>
+          <t>1969.07562687163</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977599631</t>
+          <t>1993.03209761798</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1165698681726</t>
+          <t>2104.34152733387</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964628676</t>
+          <t>2269.59777156717</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017016719317</t>
+          <t>2766.02871288664</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923186934283</t>
+          <t>2904.34434689136</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793926163139</t>
+          <t>2836.52450327835</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999331189</t>
+          <t>2794.8352078325</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660720440948</t>
+          <t>2649.90368850916</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902075880751</t>
+          <t>2375.65267642651</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694868628827</t>
+          <t>2470.79894064238</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>9628255582.31005</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>9507211395.727</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>8897511648.53659</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>8938697478.4284</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>9893238737.68779</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>9720748831.19139</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>10141432004.4635</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>11324613073.9842</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>13448253291.3962</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>14440222262.1309</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>14120556971.7678</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>14095129499.3388</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>13934793243.1911</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>12237510565.8162</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>12214823181.8329</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>8632220256.87804</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>8288166803.06965</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>7794010094.95532</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>7812567141.4287</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>8628991424.67309</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>8871541011.47508</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>8856837295.87021</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>9580608860.99699</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>11938747102.9261</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>12573434002.2763</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>12553191629.7316</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>12526281150.9111</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>12211750302.606</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>10469876308.7327</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>10248258572.6148</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>996035325.432006</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>1219044592.65735</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>1103501553.58126</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>1126130336.9997</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>1264247313.0147</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>849207819.716312</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>1284594708.59324</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>1744004212.98724</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>1509506188.47011</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1866788259.85461</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>1567365342.03613</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1568848348.4277</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>1723042940.58503</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1767634257.08347</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1966564609.21808</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>1450.05146860667</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>1445.11229905404</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>1452.13089250117</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1447.21352030129</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1450.20095865434</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1462.27211157893</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>1457.74140869849</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>1450.50582251384</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.637</t>
+          <t>1448.4262435801</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>1449.13485890453</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>1443.55946291955</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.849</t>
+          <t>1445.70502431118</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1449.34600256235</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1444.51931433683</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>1421.72699311897</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>1431.83445398875</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>1427.30241765905</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1435.31652946537</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1431.12211118966</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>1436.9631477049</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>1450.87893093097</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1447.73669810223</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1440.48394949547</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>1440.40678671357</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>1442.709962166</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>1437.94722395865</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>1441.14296810564</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>1446.10456800564</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>1441.1207861979</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>1418.14772449651</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-47.33</t>
+          <t>177513.724249902</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-47.98</t>
+          <t>173479.376536638</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-45.1</t>
+          <t>164690.676764728</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>162774.108847925</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-49.14</t>
+          <t>160458.565785168</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-49.75</t>
+          <t>161850.185048457</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-52.33</t>
+          <t>162421.29888976</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-55.52</t>
+          <t>170547.540206467</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-60.98</t>
+          <t>200681.067021766</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-65.27</t>
+          <t>238705.533185001</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-64.75</t>
+          <t>247065.800135292</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-64.27</t>
+          <t>273343.026589669</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-62.1</t>
+          <t>324688.835284459</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-56.52</t>
+          <t>375094.150818069</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-58.53</t>
+          <t>301037.714775515</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>5674284063.06236</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>5414575158.8712</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-14.17</t>
+          <t>5329692032.45312</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-13.55</t>
+          <t>5211004817.03549</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-20.39</t>
+          <t>5298917735.88017</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-22.47</t>
+          <t>5783077791.70475</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-26.66</t>
+          <t>5654245541.5193</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-32.26</t>
+          <t>5500853637.33562</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-42.6</t>
+          <t>6061406709.99908</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-46.68</t>
+          <t>6591431062.30338</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-45.48</t>
+          <t>6566844813.52142</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-44.35</t>
+          <t>7156833026.96216</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-41.91</t>
+          <t>7585897287.4447</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-34.63</t>
+          <t>9090850672.25266</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-37.88</t>
+          <t>6323996663.37484</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>155354.044170616</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>152499.637195941</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>143810.096571035</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>144436.832500273</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>141951.659026442</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>147219.957489576</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-19.02</t>
+          <t>146747.689357156</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>148688.660044613</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-46.35</t>
+          <t>175032.757146186</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-41.09</t>
+          <t>210429.495545863</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-39.59</t>
+          <t>221153.776608734</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-38.34</t>
+          <t>246146.915333527</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>292889.792187384</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>354991.525157902</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-28.69</t>
+          <t>275136.130911899</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5537.162</t>
+          <t>11881122812.5292</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5534.511</t>
+          <t>11812263637.1625</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5603.697</t>
+          <t>11369868593.1625</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>5685.502</t>
+          <t>11508080706.8669</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>5787.52</t>
+          <t>12408891245.2307</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5961.599</t>
+          <t>13331998217.7683</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6030.447</t>
+          <t>13349377136.2558</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>5990.895</t>
+          <t>13452073802.9389</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>5992.714</t>
+          <t>15774839877.1365</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>6057.565</t>
+          <t>17255660856.399</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>6122.792</t>
+          <t>17480101401.2298</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6209.157</t>
+          <t>18181393880.0551</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6331.202</t>
+          <t>18355612956.1047</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6412.834</t>
+          <t>19557266466.8268</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>6293.109</t>
+          <t>16029466086.2705</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4595.1</t>
+          <t>22159.6800792858</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4585.6</t>
+          <t>20979.7393406965</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4644.6</t>
+          <t>20880.5801936927</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4729.2</t>
+          <t>18337.2763476516</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4818.4</t>
+          <t>18506.9067587257</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4982.1</t>
+          <t>14630.227558881</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5057.8</t>
+          <t>15673.6095326039</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5033.1</t>
+          <t>21858.880161855</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5028.4</t>
+          <t>25648.3098755797</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5082.2</t>
+          <t>28276.0376391382</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>25912.0235265583</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5218.2</t>
+          <t>27196.1112561413</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5322.6</t>
+          <t>31799.0430970755</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5400.1</t>
+          <t>20102.6256601672</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5284.4</t>
+          <t>25901.5838636155</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11796.603</t>
+          <t>-6206838749.46686</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11138.413</t>
+          <t>-6397688478.2913</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10599.2</t>
+          <t>-6040176560.70942</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10776.756</t>
+          <t>-6297075889.83144</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10956.309</t>
+          <t>-7109973509.35056</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11902.348</t>
+          <t>-7548920426.06357</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11871.224</t>
+          <t>-7695131594.73646</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11498.31</t>
+          <t>-7951220165.6033</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12398.501</t>
+          <t>-9713433167.13743</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13184.423</t>
+          <t>-10664229794.0956</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12692.943</t>
+          <t>-10913256587.7083</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13673.424</t>
+          <t>-11024560853.0929</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>14224.53</t>
+          <t>-10769715668.66</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>16585.212</t>
+          <t>-10466415794.5741</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>12441.182</t>
+          <t>-9705469422.89566</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>117847.10491</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>112987.65254</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>102377.91139</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>103401.21995</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>100904.07742</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>91991.6699</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>90815.81233</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>97443.41446</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>118505.86321</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>135255.33413</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>137671.1065</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>145710.11847</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>166173.53261</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>183373.46257</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>168451.19134</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2644.885</t>
+          <t>0.0252177376472541</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2611.457</t>
+          <t>0.0221040997696612</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2622.384</t>
+          <t>0.0239110235812173</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2640.058</t>
+          <t>0.0226911958136638</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2665.412</t>
+          <t>0.0197575205565984</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2723.422</t>
+          <t>0.0197513879363492</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2734.402</t>
+          <t>0.0134594602776284</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2682.234</t>
+          <t>0.015760539970331</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2664.038</t>
+          <t>0.017362237681173</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2663.951</t>
+          <t>0.0200396786257207</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2638.288</t>
+          <t>0.0199395627427813</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2665.495</t>
+          <t>0.0198733531753056</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2695.838</t>
+          <t>0.0209864016405442</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2711.455</t>
+          <t>0.0148279366771465</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2653.904</t>
+          <t>0.00755777441618507</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>145787.436978897</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>141086.82183962</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>127201.43659137</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>129745.94339465</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>130798.806343329</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>118625.892780869</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>121459.216405026</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>133173.760639047</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>162243.029399309</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>183289.402962845</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>189538.754053939</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>200242.206394935</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>229984.011665091</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>260066.435398422</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>249276.082989467</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5790.402</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>5902.218</t>
+          <t>166925.935825279</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5705.56</t>
+          <t>150238.850509246</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5775.108</t>
+          <t>152780.082432811</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6436.424</t>
+          <t>153789.385768597</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>6791.497</t>
+          <t>139092.734411134</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>7302.144</t>
+          <t>142257.524134406</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>7876.621</t>
+          <t>155622.068038809</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>9603.645</t>
+          <t>189850.98373018</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>10185.642</t>
+          <t>214418.395190387</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10107.921</t>
+          <t>221372.722061265</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10087.969</t>
+          <t>233856.294647683</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>9732.892</t>
+          <t>268463.02295684</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>8881.205</t>
+          <t>304290.862609071</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>9184.12</t>
+          <t>291661.720887746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-20.64</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-18.6</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-18.11</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-25.14</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-26.64</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-30.74</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-36.1</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-47.64</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-50.1</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-49.11</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-48.27</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-45.31</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-39.2</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-42.46</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>172438.053732568</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>174972.110251644</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>180485.867200163</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>183477.087066379</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>192019.397675357</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>197541.591392764</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>204298.36309091</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.969</t>
+          <t>205733.840799611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>203974.716814737</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>204434.566816834</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>206651.714656127</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>211469.592023376</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>218010.089434338</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>225203.004860929</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>222432.517407521</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>145787.436978897</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>148108.679842194</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>153161.249872419</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>156268.66213584</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>164173.134836257</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>169757.696272514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>176199.126719409</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>177163.450461632</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>175487.571196141</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>176234.781917319</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>177815.765467754</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>181904.498785449</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>187670.198415123</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>193154.220820428</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>190343.137159385</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>83827.3371474317</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80070.467084721</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>73070.4469907535</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75720.8192271894</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>72656.0149914032</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>68224.621108866</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>65694.5345055935</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>71096.0202611915</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>89452.1209498204</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107950.963989613</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>114334.715688735</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>121832.704612317</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140566.39357316</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>149211.500500929</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>131472.882622254</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2644884976.88788</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2611456538.74614</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2622383522.29246</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2640057926.02361</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2665411630.59851</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2723422052.15245</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2734401947.43295</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2682234091.96582</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2664037662.86156</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2663950545.87004</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2638288062.32277</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2665494682.89325</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2695837875.11875</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2711455230.61422</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2653904109.09152</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3867180</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3877602</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3904154</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3972758</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4027605</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4108957</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4165431</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4158946</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4160432</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4198741</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4258009</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4308495</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4378108</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4449893.32227832</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4437555.55062773</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3168922</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3173179</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3198472</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3267797</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3322574</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3407095</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3469614</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3469893</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3471630</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3507058</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3563414</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3609450</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3672415</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3738337</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3716888</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>5537161563.7762</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5534510709.31955</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>5603696769.77835</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5685501816.20563</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5787519958.512</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5961599139.40131</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6030447322.11266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5990894959.81838</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5992714488.46031</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6057565469.25483</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6122792221.14095</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6209157272.36833</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6331201978.02203</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6412833763.09854</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6293109306.44956</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4595100000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4585600000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4644600000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4729200000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>4818400000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>4982100000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5057800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5033100000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5028400000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5082200000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5.144e+09</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5218200000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5322600000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5400100000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5284400000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.165843288808873</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.16971428572366</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.172865910570744</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.175109402495878</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.177047456686726</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.178402507200353</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.179995020415257</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.180132552108903</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.166563098005101</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.191720799927915</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.195351821530963</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.198012537488662</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.203713298460781</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.223534403901085</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.225223664202211</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.445526173294926</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.457877195974051</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.467406095339612</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.475852796445434</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.480561974817937</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.49979139344762</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.511218651781974</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.519639347364957</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.502523407533596</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.545194857547996</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.554528964233844</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.561598394579096</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.573414145424168</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.564980568882856</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.569376291647569</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.388630537896201</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.372408518302289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.359727994089643</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.349037801058688</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.342390568495337</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.321806099352027</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.308786327802769</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30022810052614</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.330913494461304</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.263084342524089</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.250119214235193</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.240389067932242</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.222872556115051</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.21148502721606</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.20540004415022</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.115659741544566</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.119230744064524</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.122177648215674</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.124250611989703</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.125694294726123</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.127273408489188</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.129670759247346</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.13126738276117</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.132653441270207</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.139381275156615</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.141954420237789</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.142477529378672</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.148554207443421</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.170539732797016</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.172267612866357</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.458345020135554</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.472067124700069</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.482795676750388</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.492247004959802</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.499927097718679</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.517127740576561</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.529645758851097</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.538480827969708</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.54663524183637</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.567256667411875</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.578512912924773</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.587281382681211</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.593824328538605</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.587424750347006</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.592746490029178</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.42599523831988</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.408702131235407</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.395026675033938</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.383502383050495</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.374378607555198</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.355598850934251</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.340683481901557</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.330251789269123</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.320711316893423</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.29336205743151</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.279532666837438</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.270241087940117</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.257621464017973</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.242035516855977</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.234985897104465</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>565662.49026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>551434.48693</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>507003.8431</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>522685.70802</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>523220.59463</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>492505.09565</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>496622.57662</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>526176.36293</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>637060.47889</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>745492.87068</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>783492.97772</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>848835.80683</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>978761.05105</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1103399.79032</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>972907.41524</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>256265.39088</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>246996.40291</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>223309.2975</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>228500.90166</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226445.40076</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>207317.35552</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>207952.05864</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>226718.0883</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>279303.10468</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>322369.35918</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>335707.43775</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>355688.99926</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>409029.41653</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>453502.36311</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>423134.60351</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>625363.65605692</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>642240.787117299</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>660940.924905751</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>680429.847094052</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>700182.100497513</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>721449.55282383</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>742284.419267126</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>759731.713392547</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>776340.031278286</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>796201.566599279</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>818671.25242229</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>841202.487809592</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>866528.736035931</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>892642.539159863</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>914298.655567405</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
